--- a/output/pdf_financials_xlsx/L.xlsx
+++ b/output/pdf_financials_xlsx/L.xlsx
@@ -6378,7 +6378,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>CashEquivalents</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">

--- a/output/pdf_financials_xlsx/L.xlsx
+++ b/output/pdf_financials_xlsx/L.xlsx
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="C59" s="3" t="n">
-        <v>0.000818</v>
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>1023</v>
@@ -1759,7 +1759,7 @@
         </is>
       </c>
       <c r="C61" s="3" t="n">
-        <v>0.009165</v>
+        <v>0.009983000000000001</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>9072</v>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>OtherIntangibleAssets</t>
+          <t>GoodwillAndOtherIntangibleAssets</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
